--- a/pensum/ok05/OK05_Tema_Fra_budsjett_til_kalkyle.xlsx
+++ b/pensum/ok05/OK05_Tema_Fra_budsjett_til_kalkyle.xlsx
@@ -606,7 +606,7 @@
     <t xml:space="preserve">+ Driftsomkostninger materiell</t>
   </si>
   <si>
-    <t xml:space="preserve">0 i Jan Helges enkle variant: alt indirekte ligger på lønn</t>
+    <t xml:space="preserve">0 i den enkle varianten: alt indirekte ligger på lønn</t>
   </si>
   <si>
     <t xml:space="preserve">+ Fellesomkostninger materiell</t>
@@ -729,7 +729,7 @@
     <t xml:space="preserve">Samme ting, fire navn</t>
   </si>
   <si>
-    <t xml:space="preserve">Læreboka / Jan Helge</t>
+    <t xml:space="preserve">Læreboka</t>
   </si>
   <si>
     <t xml:space="preserve">Eldata</t>

--- a/pensum/ok05/OK05_Tema_Fra_budsjett_til_kalkyle.xlsx
+++ b/pensum/ok05/OK05_Tema_Fra_budsjett_til_kalkyle.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="280">
   <si>
     <t xml:space="preserve">Fra budsjett til kalkyle — Elektro AS 2026</t>
   </si>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Kilder og forutsetninger</t>
   </si>
   <si>
-    <t xml:space="preserve">Budsjettet: «Prosjekt Bolig 3EKC/3EKD Budsjett 2026» (Elektro AS, omsetning 50 000 000). Grupperingen av kontoene i M, L, S, D og F er gjort for dette arket og kan diskuteres — det er poenget med fane 5. Lønn per time (400 kr) og timer på jobben (25) er forutsetninger for eksempelet, ikke budsjettall.</t>
+    <t xml:space="preserve">Budsjettet: «Prosjekt Bolig 3EKC/3EKD Budsjett 2026» (Elektro AS, omsetning 50 000 000). Grupperingen av kontoene i M, L, S, D og F er gjort for dette arket og kan diskuteres — det er poenget med fane 5. Timelønn (270 kr), fakturerte timer i året (29 935 = 20,2 årsverk × 1 478) og timer på jobben (25) er forutsetninger, ikke budsjettall.</t>
   </si>
   <si>
     <t xml:space="preserve">Teori: Hjertnes og Skorpen, Økonomistyring for LØM-emnet, kap. 5.2 (selvkostkalkyle for tjeneste, eksempel 3) og formelsamlingen (tilleggssats = indirekte kostnader / fordelingsgrunnlaget). Eldata: håndboken «ELdata kalkyle» (NELFO). KlarCalc: Brukerveiledning KlarCalc 2025. SmartCraft Spark: smartcraftspark.com/no (lest 19.10.2026).</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">L</t>
   </si>
   <si>
-    <t xml:space="preserve">Montørens lønn med tillegg — føres på jobben via timene</t>
+    <t xml:space="preserve">Montørens timelønn med bastillegg — «sum arbeidslønn» i Eldata</t>
   </si>
   <si>
     <t xml:space="preserve">Bastillegg</t>
@@ -171,6 +171,12 @@
     <t xml:space="preserve">Helligdagsgodtgj. produksjon</t>
   </si>
   <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sosiale kostnader på produksjonslønna: feriepenger, helligdag, sykelønn, AGA, yrkesskade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sykelønn produksjon</t>
   </si>
   <si>
@@ -201,12 +207,6 @@
     <t xml:space="preserve">Arbeidsg.avgift produksjon</t>
   </si>
   <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Følger direkte lønn: arbeidsgiveravgift og yrkesskade for produksjonen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arbeidsg.avgift adm.</t>
   </si>
   <si>
@@ -384,16 +384,16 @@
     <t xml:space="preserve">Konto 4300 − 4302 + 4500</t>
   </si>
   <si>
-    <t xml:space="preserve">L  Lønn produksjon (tariff, tillegg, feriepenger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konto 5000–5030. Dette er «sum arbeidslønn» i Eldata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S  Sosiale kostnader på produksjonslønn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S / L. Eldata: sosiale omkostninger i %</t>
+    <t xml:space="preserve">L  Lønn produksjon (timelønn + bastillegg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konto 5000 og 5002. «Sum arbeidslønn» i Eldata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S  Sosiale kostnader (ferie, helligdag, syk, AGA, yrkesskade)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eldata S = all produksjonslønn / (timelønn × fakturerte timer) − 1. Per fakturert time, slik at timer som ikke faktureres også dekkes</t>
   </si>
   <si>
     <t xml:space="preserve">= Direkte lønn (bokas begrep)</t>
@@ -456,6 +456,42 @@
     <t xml:space="preserve">Skal være 0. Er det ikke 0, har en konto fått en gruppe som ikke finnes.</t>
   </si>
   <si>
+    <t xml:space="preserve">Timelønn (tariff + tillegg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forutsetning fra Eldata-arket (gjennomsnittlig timelønn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fakturerte timer i året</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forutsetning: 9 200 000 / (270 × 1 680) = 20,2 årsverk × 1 478 fakturerte timer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satsene i kroner per fakturert time (Eldata godtar begge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S sosiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D drift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F felles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timekost = timelønn + S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selvkost per time = timekost + D + F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timepris til kunden = selvkost × (1 + P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faktor arbeid = timepris / timelønn</t>
+  </si>
+  <si>
     <t xml:space="preserve">Selvkostkalkyle for én jobb — slik boka gjør det</t>
   </si>
   <si>
@@ -465,10 +501,10 @@
     <t xml:space="preserve">Forutsetninger for jobben</t>
   </si>
   <si>
-    <t xml:space="preserve">Timer på jobben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lønn per time (tariff + tillegg, uten sosiale)</t>
+    <t xml:space="preserve">Fakturerte timer på jobben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timelønn (fra fane 2)</t>
   </si>
   <si>
     <t xml:space="preserve">Materiell, netto innkjøpspris</t>
@@ -859,11 +895,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -998,7 +1035,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1060,6 +1097,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1657,10 +1698,10 @@
         <v>400000</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1668,16 +1709,16 @@
         <v>5020</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>300000</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1685,16 +1726,16 @@
         <v>5030</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>1200000</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1702,16 +1743,16 @@
         <v>5100</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>3600000</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1719,16 +1760,16 @@
         <v>5120</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>75000</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1736,16 +1777,16 @@
         <v>5130</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>450000</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1753,16 +1794,16 @@
         <v>5211</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>100000</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1770,16 +1811,16 @@
         <v>5945</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>650000</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1787,16 +1828,16 @@
         <v>5400</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>1600000</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1810,10 +1851,10 @@
         <v>700000</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1827,10 +1868,10 @@
         <v>600000</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1844,10 +1885,10 @@
         <v>-300000</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1861,10 +1902,10 @@
         <v>60000</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1895,10 +1936,10 @@
         <v>100000</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1929,10 +1970,10 @@
         <v>750000</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1946,10 +1987,10 @@
         <v>60000</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1963,10 +2004,10 @@
         <v>100000</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1980,10 +2021,10 @@
         <v>20000</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1997,10 +2038,10 @@
         <v>15000</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2116,10 +2157,10 @@
         <v>150000</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2133,10 +2174,10 @@
         <v>50000</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2150,10 +2191,10 @@
         <v>75000</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2167,10 +2208,10 @@
         <v>125000</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2184,10 +2225,10 @@
         <v>50000</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2201,10 +2242,10 @@
         <v>20000</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2218,10 +2259,10 @@
         <v>10000</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2235,10 +2276,10 @@
         <v>50000</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2252,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2269,10 +2310,10 @@
         <v>10000</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2303,10 +2344,10 @@
         <v>15000</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2320,10 +2361,10 @@
         <v>15000</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2422,10 +2463,10 @@
         <v>180000</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2473,10 +2514,10 @@
         <v>200000</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2490,10 +2531,10 @@
         <v>100000</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2507,10 +2548,10 @@
         <v>125000</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2558,10 +2599,10 @@
         <v>200000</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2624,7 +2665,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -2670,23 +2711,23 @@
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">SUMIF('1 Budsjett'!$D$5:$D$68,"L",'1 Budsjett'!$C$5:$C$68)</f>
-        <v>11100000</v>
+        <v>9200000</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>113</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">SUMIF('1 Budsjett'!$D$5:$D$68,"S",'1 Budsjett'!$C$5:$C$68)</f>
-        <v>1660000</v>
+        <v>3560000</v>
       </c>
       <c r="C6" s="12" t="n">
-        <f aca="false">B6/B5</f>
-        <v>0.14954954954955</v>
+        <f aca="false">B7/(B20*B21)-1</f>
+        <v>0.578729221956214</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>114</v>
@@ -2828,6 +2869,96 @@
       </c>
       <c r="D19" s="7" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>29935</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <f aca="false">B20*C6</f>
+        <v>156.256889928178</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <f aca="false">B8/B21</f>
+        <v>83.1802238182729</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <f aca="false">B9/B21</f>
+        <v>277.100384165692</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <f aca="false">B20+C24</f>
+        <v>426.256889928178</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <f aca="false">C27+C25+C26</f>
+        <v>786.537497912143</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <f aca="false">C28*(1+C12)</f>
+        <v>877.93001218009</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <f aca="false">C29/B20</f>
+        <v>3.25159263770404</v>
       </c>
     </row>
   </sheetData>
@@ -2856,12 +2987,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2869,12 +3000,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>25</v>
@@ -2882,15 +3013,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>400</v>
+        <v>151</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <f aca="false">'2 Satser'!B20</f>
+        <v>270</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>10000</v>
@@ -2898,169 +3030,169 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="16" t="n">
+        <v>153</v>
+      </c>
+      <c r="B8" s="17" t="n">
         <f aca="false">'2 Satser'!C6</f>
-        <v>0.14954954954955</v>
+        <v>0.578729221956214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B9" s="16" t="n">
+        <v>154</v>
+      </c>
+      <c r="B9" s="17" t="n">
         <f aca="false">'2 Satser'!C10</f>
         <v>0.845219435736677</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="16" t="n">
+        <v>155</v>
+      </c>
+      <c r="B10" s="17" t="n">
         <f aca="false">'2 Satser'!C12</f>
         <v>0.116196004018306</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" s="17" t="n">
+        <v>156</v>
+      </c>
+      <c r="B11" s="18" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>106</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C14" s="15" t="n">
         <f aca="false">B5*B6*(1+B8)</f>
-        <v>11495.4954954955</v>
+        <v>10656.4222482044</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C15" s="15" t="n">
         <f aca="false">B7</f>
         <v>10000</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="18" t="n">
+        <v>163</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <f aca="false">C14+C15</f>
-        <v>21495.4954954955</v>
+        <v>20656.4222482044</v>
       </c>
       <c r="D16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">C14*B9</f>
-        <v>9716.21621621622</v>
+        <v>9007.01519959913</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="18" t="n">
+        <v>166</v>
+      </c>
+      <c r="C18" s="19" t="n">
         <f aca="false">C16+C17</f>
-        <v>31211.7117117117</v>
+        <v>29663.4374478036</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">C18*B10</f>
-        <v>3626.67617947225</v>
+        <v>3446.77289688174</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C20" s="18" t="n">
+        <v>170</v>
+      </c>
+      <c r="C20" s="19" t="n">
         <f aca="false">C18+C19</f>
-        <v>34838.387891184</v>
+        <v>33110.2103446853</v>
       </c>
       <c r="D20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C21" s="15" t="n">
         <f aca="false">C20*B11</f>
-        <v>8709.59697279599</v>
+        <v>8277.55258617133</v>
       </c>
       <c r="D21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="18" t="n">
+        <v>172</v>
+      </c>
+      <c r="C22" s="19" t="n">
         <f aca="false">C20+C21</f>
-        <v>43547.98486398</v>
+        <v>41387.7629308566</v>
       </c>
       <c r="D22" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C24" s="15" t="n">
         <f aca="false">B6*(1+B8)</f>
-        <v>459.81981981982</v>
+        <v>426.256889928178</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">B6*(1+B8)*(1+B9)*(1+B10)</f>
-        <v>947.057114040036</v>
+        <v>877.93001218009</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3094,12 +3226,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3108,151 +3240,151 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D5" s="11" t="n">
         <f aca="false">'3 Kalkyle bok'!B5*'3 Kalkyle bok'!B6</f>
-        <v>10000</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6" s="16" t="n">
+        <v>183</v>
+      </c>
+      <c r="B6" s="17" t="n">
         <f aca="false">'2 Satser'!C6</f>
-        <v>0.14954954954955</v>
+        <v>0.578729221956214</v>
       </c>
       <c r="C6" s="15" t="n">
         <f aca="false">D5*B6</f>
-        <v>1495.4954954955</v>
+        <v>3906.42224820444</v>
       </c>
       <c r="D6" s="15" t="n">
         <f aca="false">D5+C6</f>
-        <v>11495.4954954955</v>
+        <v>10656.4222482044</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="16" t="n">
+        <v>185</v>
+      </c>
+      <c r="B7" s="17" t="n">
         <f aca="false">'2 Satser'!C8</f>
         <v>0.195141065830721</v>
       </c>
       <c r="C7" s="15" t="n">
         <f aca="false">D6*B7</f>
-        <v>2243.24324324324</v>
+        <v>2079.50559545682</v>
       </c>
       <c r="D7" s="15" t="n">
         <f aca="false">D6+C7</f>
-        <v>13738.7387387387</v>
+        <v>12735.9278436613</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="16" t="n">
+        <v>187</v>
+      </c>
+      <c r="B8" s="17" t="n">
         <f aca="false">'2 Satser'!C9</f>
         <v>0.543934426229508</v>
       </c>
       <c r="C8" s="15" t="n">
         <f aca="false">D7*B8</f>
-        <v>7472.97297297297</v>
+        <v>6927.50960414231</v>
       </c>
       <c r="D8" s="15" t="n">
         <f aca="false">D7+C8</f>
-        <v>21211.7117117117</v>
+        <v>19663.4374478036</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="B9" s="17" t="n">
         <f aca="false">'2 Satser'!C12</f>
         <v>0.116196004018306</v>
       </c>
       <c r="C9" s="15" t="n">
         <f aca="false">D8*B9</f>
-        <v>2464.71613928919</v>
+        <v>2284.81285669869</v>
       </c>
       <c r="D9" s="15" t="n">
         <f aca="false">D8+C9</f>
-        <v>23676.4278510009</v>
+        <v>21948.2503045023</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="18" t="n">
+        <v>191</v>
+      </c>
+      <c r="D10" s="19" t="n">
         <f aca="false">D9</f>
-        <v>23676.4278510009</v>
+        <v>21948.2503045023</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">D10/D5</f>
-        <v>2.36764278510009</v>
+        <v>3.25159263770404</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D14" s="11" t="n">
         <f aca="false">'3 Kalkyle bok'!B7</f>
@@ -3261,9 +3393,9 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" s="17" t="n">
+        <v>196</v>
+      </c>
+      <c r="B15" s="18" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="15" t="n">
@@ -3275,14 +3407,14 @@
         <v>10000</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="17" t="n">
+        <v>198</v>
+      </c>
+      <c r="B16" s="18" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="15" t="n">
@@ -3294,14 +3426,14 @@
         <v>10000</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B17" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="B17" s="17" t="n">
         <f aca="false">'2 Satser'!C12</f>
         <v>0.116196004018306</v>
       </c>
@@ -3314,21 +3446,21 @@
         <v>11161.9600401831</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="18" t="n">
+        <v>201</v>
+      </c>
+      <c r="D18" s="19" t="n">
         <f aca="false">D17</f>
         <v>11161.9600401831</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">D18/D14</f>
@@ -3337,67 +3469,67 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D21" s="10" t="n">
         <f aca="false">D10+D18</f>
-        <v>34838.387891184</v>
+        <v>33110.2103446853</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D22" s="11" t="n">
         <f aca="false">'3 Kalkyle bok'!C20</f>
-        <v>34838.387891184</v>
+        <v>33110.2103446853</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">D21-D22</f>
         <v>0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D26" s="15" t="n">
         <f aca="false">D21-D14-D6</f>
-        <v>13342.8923956885</v>
+        <v>12453.7880964809</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D27" s="15" t="n">
         <f aca="false">D26-C7-C15</f>
-        <v>11099.6491524452</v>
+        <v>10374.282501024</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D28" s="15" t="n">
         <f aca="false">D27-C8-C16</f>
-        <v>3626.67617947225</v>
+        <v>3446.77289688174</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3428,12 +3560,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3442,15 +3574,15 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>5000</v>
@@ -3461,7 +3593,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>40000</v>
@@ -3472,16 +3604,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="D8" s="16" t="n">
+        <v>218</v>
+      </c>
+      <c r="D8" s="17" t="n">
         <f aca="false">'2 Satser'!C10</f>
         <v>0.845219435736677</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">B5*$D$8</f>
@@ -3494,7 +3626,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">B5+B6+B9</f>
@@ -3507,19 +3639,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">'2 Satser'!B10/('2 Satser'!B4+'2 Satser'!B7)</f>
         <v>0.317112613937077</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">(B5+B6)*$D$12</f>
@@ -3532,7 +3664,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">B5+B6+B13</f>
@@ -3545,7 +3677,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">B14-B10</f>
@@ -3558,12 +3690,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -3601,23 +3733,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -3626,14 +3758,14 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="19"/>
+        <v>231</v>
+      </c>
+      <c r="C5" s="20"/>
       <c r="D5" s="6" t="str">
         <f aca="false">IF(C5="","",IF(ABS(C5-E5)&lt;=0.002,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="21" t="n">
         <f aca="false">'2 Satser'!C10</f>
         <v>0.845219435736677</v>
       </c>
@@ -3643,9 +3775,9 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="21"/>
+        <v>232</v>
+      </c>
+      <c r="C6" s="22"/>
       <c r="D6" s="6" t="str">
         <f aca="false">IF(C6="","",IF(ABS(C6-E6)&lt;=50,"Riktig","Prøv igjen"))</f>
         <v/>
@@ -3660,9 +3792,9 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="21"/>
+        <v>233</v>
+      </c>
+      <c r="C7" s="22"/>
       <c r="D7" s="6" t="str">
         <f aca="false">IF(C7="","",IF(ABS(C7-E7)&lt;=50,"Riktig","Prøv igjen"))</f>
         <v/>
@@ -3677,16 +3809,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C8" s="22"/>
+        <v>234</v>
+      </c>
+      <c r="C8" s="23"/>
       <c r="D8" s="6" t="str">
         <f aca="false">IF(C8="","",IF(ABS(C8-E8)&lt;=0.002,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">(1+'2 Satser'!C6)*(1+'2 Satser'!C10)*(1+'2 Satser'!C12)</f>
-        <v>2.36764278510009</v>
+        <v>3.25159263770404</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3694,21 +3826,21 @@
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C9" s="19"/>
+        <v>235</v>
+      </c>
+      <c r="C9" s="20"/>
       <c r="D9" s="6" t="str">
         <f aca="false">IF(C9="","",IF(ABS(C9-E9)&lt;=0.005,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">('2 Satser'!B10-3600000)/('2 Satser'!B7+3600000)</f>
         <v>0.439180929095355</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3735,55 +3867,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>110</v>
@@ -3791,109 +3923,109 @@
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>

--- a/pensum/ok05/OK05_Tema_Fra_budsjett_til_kalkyle.xlsx
+++ b/pensum/ok05/OK05_Tema_Fra_budsjett_til_kalkyle.xlsx
@@ -1035,7 +1035,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1134,6 +1134,10 @@
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1405,7 +1409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1418,7 +1422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
@@ -1433,7 +1437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1461,7 +1465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
@@ -1474,12 +1478,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
@@ -2717,7 +2721,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>113</v>
       </c>
@@ -2838,7 +2842,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
         <v>130</v>
       </c>
@@ -3074,7 +3078,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
         <v>159</v>
       </c>
@@ -3238,7 +3242,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>178</v>
       </c>
@@ -3248,7 +3252,7 @@
       <c r="C4" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c s="25" r="D4" t="s">
         <v>180</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -3365,7 +3369,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>194</v>
       </c>
@@ -3375,7 +3379,7 @@
       <c r="C13" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c s="25" r="D13" t="s">
         <v>180</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -3410,7 +3414,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
         <v>198</v>
       </c>
@@ -3520,7 +3524,7 @@
         <v>10374.282501024</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
         <v>210</v>
       </c>
@@ -3572,8 +3576,8 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
+    <row ht="27" customHeight="true" r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="25" r="B4" t="s">
         <v>214</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -3736,7 +3740,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
         <v>227</v>
       </c>
@@ -3838,7 +3842,7 @@
         <v>0.439180929095355</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="52.5" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>236</v>
       </c>
@@ -3870,7 +3874,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>238</v>
       </c>
@@ -3880,14 +3884,14 @@
       <c r="C3" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c s="25" r="D3" t="s">
         <v>241</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="64.5" customHeight="true" r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>243</v>
       </c>
@@ -3904,7 +3908,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="52.5" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>248</v>
       </c>
@@ -3921,7 +3925,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="64.5" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>252</v>
       </c>
@@ -3955,7 +3959,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="52.5" customHeight="true" r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>169</v>
       </c>
@@ -3972,7 +3976,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="64.5" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>265</v>
       </c>
@@ -4023,7 +4027,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="52.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>279</v>
       </c>
